--- a/TC_Manager_Full_Regression_Checklist.xlsx
+++ b/TC_Manager_Full_Regression_Checklist.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10354,6 +10354,184 @@
         </is>
       </c>
       <c r="O175" s="6" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>160</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>TC-TR-031</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>우선순위 멀티 선택</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>런 데이터 존재, 우선순위가 2종 이상</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>1. Priority 필터 버튼을 누른다.
+2. 우선순위 두 개를 체크한다.
+3. 체크를 하나 풀어 본다.</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>1. 체크박스 목록이 펼쳐진다.
+2. 고른 우선순위 중 하나라도 맞는 행만 남는다.
+3. 버튼에 "Priority: 2개"가 표시되고 하나만 남기면 그 값이 표시된다.
+4. 바깥을 클릭하거나 Esc 를 누르면 닫힌다.</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>161</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>TC-TR-032</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>우선순위 미지정</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>우선순위가 빈 TC 가 1건 이상 포함된 런</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>1. Priority 필터 버튼을 누른다.
+2. 목록 맨 아래 (미지정) 을 체크한다.</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>1. 우선순위가 빈 TC 가 있을 때만 (미지정) 항목이 나타난다.
+2. 체크하면 우선순위가 빈 행만 남는다.
+3. 버튼에 "Priority: (미지정)"이 표시된다.</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>162</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>TC-TR-033</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>테스트 런</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>시트 이동 시 선택 유지</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>시트별 우선순위 구성이 다른 런</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>1. A 시트에서 그 시트에만 있는 우선순위를 체크한다.
+2. 그 우선순위가 없는 B 시트 탭으로 옮긴다.
+3. Priority 필터 버튼을 눌러 목록을 확인한다.</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>1. 그리드는 조건에 맞는 행이 없어 비어 있다.
+2. 목록에 이전에 고른 우선순위가 체크된 채로 남아 있어 해제할 수 있다.
+3. 해제하면 B 시트의 행이 다시 보인다.
+4. 시트를 옮길 때 열려 있던 드롭다운은 닫힌다.</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
